--- a/artfynd/A 56183-2025 artfynd.xlsx
+++ b/artfynd/A 56183-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129844728</v>
       </c>
       <c r="B2" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129844727</v>
       </c>
       <c r="B3" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129844710</v>
       </c>
       <c r="B4" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,30 +1023,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129844715</v>
+        <v>129844711</v>
       </c>
       <c r="B5" t="n">
-        <v>91613</v>
+        <v>91561</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
@@ -1061,7 +1065,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Röda jorden, Riddarhyttan , Vstm</t>
+          <t>Röda jorden, Riddarhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1100,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På grövre högstubbe av gran samt de lägre stamdelarna.</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129844711</v>
+        <v>129844703</v>
       </c>
       <c r="B6" t="n">
-        <v>91557</v>
+        <v>8439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,21 +1152,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,12 +1174,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1188,13 +1189,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529652</v>
+        <v>529657</v>
       </c>
       <c r="R6" t="n">
-        <v>6626649</v>
+        <v>6626656</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129844703</v>
+        <v>129844704</v>
       </c>
       <c r="B7" t="n">
-        <v>8439</v>
+        <v>83033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,34 +1272,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1308,13 +1303,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529657</v>
+        <v>529705</v>
       </c>
       <c r="R7" t="n">
-        <v>6626656</v>
+        <v>6626662</v>
       </c>
       <c r="S7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1343,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,7 +1348,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,125 +1377,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>129844704</v>
-      </c>
-      <c r="B8" t="n">
-        <v>83033</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6439</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Gulnål</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Röda jorden, Riddarhyttan, Vstm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>529705</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6626662</v>
-      </c>
-      <c r="S8" t="n">
-        <v>21</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Skinnskatteberg</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Skinnskatteberg</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På högstubbe av björk.</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56183-2025 artfynd.xlsx
+++ b/artfynd/A 56183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844728</v>
       </c>
       <c r="B2" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129844727</v>
       </c>
       <c r="B3" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129844710</v>
       </c>
       <c r="B4" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129844711</v>
       </c>
       <c r="B5" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>129844704</v>
       </c>
       <c r="B7" t="n">
-        <v>83033</v>
+        <v>83035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56183-2025 artfynd.xlsx
+++ b/artfynd/A 56183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844728</v>
       </c>
       <c r="B2" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129844727</v>
       </c>
       <c r="B3" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56183-2025 artfynd.xlsx
+++ b/artfynd/A 56183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844728</v>
       </c>
       <c r="B2" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129844727</v>
       </c>
       <c r="B3" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129844710</v>
       </c>
       <c r="B4" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129844711</v>
       </c>
       <c r="B5" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>129844704</v>
       </c>
       <c r="B7" t="n">
-        <v>83035</v>
+        <v>83038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56183-2025 artfynd.xlsx
+++ b/artfynd/A 56183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844728</v>
       </c>
       <c r="B2" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129844727</v>
       </c>
       <c r="B3" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129844710</v>
       </c>
       <c r="B4" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129844711</v>
       </c>
       <c r="B5" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>129844703</v>
       </c>
       <c r="B6" t="n">
-        <v>8439</v>
+        <v>8440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>129844704</v>
       </c>
       <c r="B7" t="n">
-        <v>83038</v>
+        <v>83041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56183-2025 artfynd.xlsx
+++ b/artfynd/A 56183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844728</v>
       </c>
       <c r="B2" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129844727</v>
       </c>
       <c r="B3" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129844710</v>
       </c>
       <c r="B4" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129844711</v>
       </c>
       <c r="B5" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>129844704</v>
       </c>
       <c r="B7" t="n">
-        <v>83041</v>
+        <v>83042</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56183-2025 artfynd.xlsx
+++ b/artfynd/A 56183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844728</v>
       </c>
       <c r="B2" t="n">
-        <v>97044</v>
+        <v>97061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129844727</v>
       </c>
       <c r="B3" t="n">
-        <v>97044</v>
+        <v>97061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129844710</v>
       </c>
       <c r="B4" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129844711</v>
       </c>
       <c r="B5" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>129844704</v>
       </c>
       <c r="B7" t="n">
-        <v>83042</v>
+        <v>83048</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56183-2025 artfynd.xlsx
+++ b/artfynd/A 56183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844728</v>
       </c>
       <c r="B2" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129844727</v>
       </c>
       <c r="B3" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129844710</v>
       </c>
       <c r="B4" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129844711</v>
       </c>
       <c r="B5" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56183-2025 artfynd.xlsx
+++ b/artfynd/A 56183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844728</v>
       </c>
       <c r="B2" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129844727</v>
       </c>
       <c r="B3" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129844710</v>
       </c>
       <c r="B4" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129844711</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>129844704</v>
       </c>
       <c r="B7" t="n">
-        <v>83056</v>
+        <v>83141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56183-2025 artfynd.xlsx
+++ b/artfynd/A 56183-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129844728</v>
+        <v>129844727</v>
       </c>
       <c r="B2" t="n">
-        <v>97079</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529553</v>
+        <v>529705</v>
       </c>
       <c r="R2" t="n">
-        <v>6626616</v>
+        <v>6626662</v>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129844727</v>
+        <v>129844728</v>
       </c>
       <c r="B3" t="n">
-        <v>97079</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529705</v>
+        <v>529553</v>
       </c>
       <c r="R3" t="n">
-        <v>6626662</v>
+        <v>6626616</v>
       </c>
       <c r="S3" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +908,7 @@
         <v>129844710</v>
       </c>
       <c r="B4" t="n">
-        <v>91605</v>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129844711</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129844703</v>
+        <v>129844704</v>
       </c>
       <c r="B6" t="n">
-        <v>8440</v>
+        <v>83290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,34 +1152,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1189,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529657</v>
+        <v>529705</v>
       </c>
       <c r="R6" t="n">
-        <v>6626656</v>
+        <v>6626662</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129844704</v>
+        <v>129844703</v>
       </c>
       <c r="B7" t="n">
-        <v>83056</v>
+        <v>8444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,28 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1303,13 +1308,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529705</v>
+        <v>529657</v>
       </c>
       <c r="R7" t="n">
-        <v>6626662</v>
+        <v>6626656</v>
       </c>
       <c r="S7" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,12 +1353,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På högstubbe av björk.</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
